--- a/data/05_modelado/results/results_otros.xlsx
+++ b/data/05_modelado/results/results_otros.xlsx
@@ -563,7 +563,7 @@
         <v>0.8771934502274092</v>
       </c>
       <c r="K2" t="n">
-        <v>6.912</v>
+        <v>3.299</v>
       </c>
       <c r="L2" t="n">
         <v>6.91</v>
@@ -628,7 +628,7 @@
         <v>0.8771934502274092</v>
       </c>
       <c r="K3" t="n">
-        <v>5.686</v>
+        <v>4.374</v>
       </c>
       <c r="L3" t="n">
         <v>6.64</v>
@@ -693,7 +693,7 @@
         <v>0.8438055469742929</v>
       </c>
       <c r="K4" t="n">
-        <v>13.685</v>
+        <v>7.661</v>
       </c>
       <c r="L4" t="n">
         <v>6.64</v>
@@ -758,10 +758,10 @@
         <v>0.83499391479048</v>
       </c>
       <c r="K5" t="n">
-        <v>0.286</v>
+        <v>0.238</v>
       </c>
       <c r="L5" t="n">
-        <v>6.63</v>
+        <v>6.77</v>
       </c>
       <c r="M5" t="n">
         <v>0.7239</v>
@@ -823,10 +823,10 @@
         <v>0.83499391479048</v>
       </c>
       <c r="K6" t="n">
-        <v>0.331</v>
+        <v>0.226</v>
       </c>
       <c r="L6" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
       <c r="M6" t="n">
         <v>0.7239</v>
@@ -888,7 +888,7 @@
         <v>0.8206795392518476</v>
       </c>
       <c r="K7" t="n">
-        <v>2.696</v>
+        <v>1.221</v>
       </c>
       <c r="L7" t="n">
         <v>6.64</v>
@@ -953,7 +953,7 @@
         <v>0.8250666470391879</v>
       </c>
       <c r="K8" t="n">
-        <v>1.685</v>
+        <v>0.828</v>
       </c>
       <c r="L8" t="n">
         <v>6.64</v>
@@ -1018,10 +1018,10 @@
         <v>0.8223895764265686</v>
       </c>
       <c r="K9" t="n">
-        <v>5.223</v>
+        <v>2.635</v>
       </c>
       <c r="L9" t="n">
-        <v>6.63</v>
+        <v>6.77</v>
       </c>
       <c r="M9" t="n">
         <v>0.6951000000000001</v>
@@ -1083,7 +1083,7 @@
         <v>0.8223895764265686</v>
       </c>
       <c r="K10" t="n">
-        <v>3.378</v>
+        <v>2.048</v>
       </c>
       <c r="L10" t="n">
         <v>6.63</v>
